--- a/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8214</v>
+        <v>0.8519</v>
       </c>
       <c r="C2" t="n">
         <v>0.6216</v>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8333</v>
+        <v>0.8696</v>
       </c>
       <c r="C3" t="n">
         <v>0.6897</v>
@@ -491,7 +491,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8555</v>
+        <v>0.8958</v>
       </c>
     </row>
     <row r="7">
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8445</v>
+        <v>0.8265</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6522</v>
+        <v>0.7826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -664,13 +664,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6667</v>
+        <v>0.8</v>
       </c>
       <c r="F3" t="n">
         <v>0.5</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8214</v>
+        <v>0.8519</v>
       </c>
     </row>
     <row r="9">
@@ -880,7 +880,7 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
@@ -936,7 +936,7 @@
         <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
         <v>23</v>
@@ -964,7 +964,7 @@
         <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>20</v>
@@ -976,7 +976,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
         <v>23</v>
@@ -992,7 +992,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
         <v>23</v>
@@ -1004,7 +1004,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
         <v>23</v>
@@ -1020,7 +1020,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
@@ -1185,171 +1185,171 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M04_AU23</t>
+          <t>CF_M04_AU25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7707000000000001</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Data Layer (Frontend)</t>
-        </is>
-      </c>
+        <v>0.7562</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Handles data access, including calls to the backend, data transformation, and concrete implementation of repositories.</t>
+          <t>The persistence of data is carried out through a MySQL relational database, managed through the Django ORM.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02', 'AU_13']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>backend, mysql</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
+          <t>In the back-end, HTTP requests received by Django views are delegated to the corresponding use cases, which encapsulate the business logic and use repositories to access the database or external services.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M04_P08</t>
+          <t>CF_M04_AU04, CF_M04_AU10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M04_AU23</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>CF_M04_AU25</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>backend, database</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M04_AU25</t>
+          <t>CF_M04_AU23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7862</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>0.7707000000000001</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Data Layer (Frontend)</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>The back-end is implemented using Django [...] The persistence of data is performed through a MySQL relational database.</t>
+          <t>Responsible for data access, including backend calls, data transformation, and concrete implementation of repositories.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_11']</t>
+          <t>['AU_01']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>backend, mysql</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>In the back-end, HTTP requests received by Django views are delegated to the corresponding use cases, which encapsulate the business logic and use repositories to access the database or external services.</t>
+          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M04_AU04, CF_M04_AU10</t>
+          <t>CF_M04_P08</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M04_AU25</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>backend, database</t>
-        </is>
-      </c>
+          <t>CF_M04_AU23</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1431,63 +1431,67 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M04_AU29</t>
+          <t>CF_M04_AU08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8167</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>0.914</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Application Layer (Backend)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The frontend is the mobile application developed with Flutter that manages the graphical interface, navigation, and user interaction [...] The communication between the front-end and the back-end is performed through a REST API.</t>
+          <t>Includes the system's use cases, which orchestrate business logic and define the flow of operations, acting as an intermediary between the domain and infrastructure.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>54,55</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_01', 'AU_02']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>frontend, backend</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Application Layer</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
+          <t>Application Layer: includes the system use cases, which orchestrate the business logic and define the flow of operations</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1495,30 +1499,26 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M04_AU01, CF_M04_AU04</t>
+          <t>CF_M04_P01</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M04_AU29</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>frontend, backend</t>
-        </is>
-      </c>
+          <t>CF_M04_AU08</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M04_AU08</t>
+          <t>CF_M04_AU09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1527,11 +1527,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.914</v>
+        <v>0.9141</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Application Layer (Backend)</t>
+          <t>Infrastructure Layer (Backend)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Includes the system's use cases, which orchestrate business logic and define the flow of operations.</t>
+          <t>Responsible for interaction with the exterior, implementing Django HTTP views, repositories that access the database via ORM, and adapters for external services.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>55, 65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1557,13 +1557,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Application Layer</t>
+          <t>Infrastructure Layer</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Application Layer: includes the system use cases, which orchestrate the business logic and define the flow of operations</t>
+          <t>Infrastructure Layer: This is responsible for interaction with the outside world.</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1587,7 +1587,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M04_AU08</t>
+          <t>CF_M04_AU09</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1595,12 +1595,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M04_AU09</t>
+          <t>CF_M04_AU07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1609,11 +1609,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9141</v>
+        <v>0.9246</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Infrastructure Layer (Backend)</t>
+          <t>Domain Layer (Backend)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Responsible for interaction with the exterior, including HTTP views, database repositories, and external service adapters.</t>
+          <t>Contains the purest business logic of the system, as well as domain models and repository interfaces, independent of Django, the database, or any external service.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>55, 65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1639,13 +1639,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Infrastructure Layer</t>
+          <t>Domain Layer</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Infrastructure Layer: This is responsible for interaction with the outside world.</t>
+          <t>Domain Layer: contains the purest business logic of the system, as well as the domain models and repositories interfaces.</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1669,7 +1669,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M04_AU09</t>
+          <t>CF_M04_AU07</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1677,67 +1677,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M04_AU07</t>
+          <t>CF_M04_AU15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9246</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Domain Layer (Backend)</t>
-        </is>
-      </c>
+        <v>0.9341</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Contains the purest business logic of the system, including domain models and repository interfaces.</t>
+          <t>The back-end integrates several external services, such as artificial intelligence services (Gemini or ChatGPT) and authentication services.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>55, 65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_02', 'AU_09', 'AU_10']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_06</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Domain Layer</t>
-        </is>
-      </c>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>backend, authentication service, ai service</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Domain Layer: contains the purest business logic of the system, as well as the domain models and repositories interfaces.</t>
+          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1745,21 +1741,25 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M04_P01</t>
+          <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M04_AU07</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>CF_M04_AU15</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>frontend, gemini</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Manages the state of the application and the communication with the user interface using Bloc/Cubit.</t>
+          <t>Manages the application state and communication with the user interface using Bloc/Cubit.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1803,7 +1803,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1841,12 +1841,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M04_AU15</t>
+          <t>CF_M04_AU29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9637</v>
+        <v>0.9972</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT) and authentication services.</t>
+          <t>The communication between the front-end and the back-end is carried out through a REST API, using JSON format messages for both requests and responses.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1875,18 +1875,18 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_12']</t>
+          <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>backend, ai service</t>
+          <t>frontend, backend</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
+          <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1905,25 +1905,25 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
+          <t>CF_M04_AU01, CF_M04_AU04</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M04_AU15</t>
+          <t>CF_M04_AU29</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>frontend, gemini</t>
+          <t>frontend, backend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The frontend follows the principles of Clean Architecture, applied strictly to organize code into Presentation, Domain, and Data layers.</t>
+          <t>The frontend follows the principles of Clean Architecture, separating responsibilities into Presentation, Domain, and Data layers.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1963,7 +1963,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55, 56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2045,7 +2045,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2111,23 +2111,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The communication between the front-end and the back-end is performed through a REST API.</t>
+          <t>Communication protocol used between frontend and backend.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55, 66</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_16']</t>
+          <t>['AU_19']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2165,12 +2165,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M04_AU27</t>
+          <t>CF_M04_AU18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2183,22 +2183,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Used for complementary functionalities like notifications.</t>
+          <t>Service responsible for managing user authentication, including delegated login and OTP generation.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2209,13 +2209,13 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Firebase for complementary functionalities (notifications, services associated).</t>
+          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M04_AU27</t>
+          <t>CF_M04_AU18</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2271,23 +2271,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The communication is performed through a REST API based on HTTP.</t>
+          <t>Communication protocol used for API requests.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>66, 70</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_16']</t>
+          <t>['AU_19']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The backend is the software responsible for processing user requests, business logic, and data persistence.</t>
+          <t>The backend is the software responsible for processing user requests, business logic, data persistence, and integration with external services.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54, 55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The frontend is the mobile application developed with Flutter that manages the graphical interface, navigation, and user interaction.</t>
+          <t>The frontend is the mobile application developed with Flutter that acts as the presentation layer, managing the graphical interface, navigation, and user interaction.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Framework used as the main backend for building the REST API.</t>
+          <t>Backend framework used for building the REST API.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55, 56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2665,23 +2665,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AI service provider used for generating review responses.</t>
+          <t>AI service integrated for generating review responses.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55, 68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_12', 'AU_18']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -2715,7 +2715,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2759,7 +2759,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,23 +2825,23 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AI service provider used for generating review responses.</t>
+          <t>AI service integrated for generating review responses.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55, 56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_12', 'AU_18']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54, 56</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2999,7 +2999,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3045,7 +3045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3093,7 +3093,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3109,7 +3109,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>External service for artificial intelligence suggestions.</t>
+          <t>External service used for generating intelligent response suggestions for reviews.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3125,7 +3125,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3136,26 +3136,26 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>backend, firebase</t>
+          <t>frontend, backend</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Firebase, used for complementary functionalities like notifications.</t>
+          <t>The frontend is the mobile application developed with Flutter that acts as the presentation layer [...] and of performing the necessary requests to the back-end to obtain or modify information.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M04_AU27</t>
+          <t>CF_M04_AU01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8454</v>
+        <v>0.7971</v>
       </c>
     </row>
     <row r="4">
@@ -3177,7 +3177,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data is exchanged in JSON format, using standard HTTP methods like GET and POST.</t>
+          <t>The communication between the front-end and the back-end is carried out through a REST API, using JSON format messages for both requests and responses.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3209,7 +3209,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The system architecture is based on a mobile application (frontend) that makes requests to a backend server.</t>
+          <t>The system follows a client-server architecture where the mobile application (frontend) makes requests to a server (backend) that processes them.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3224,42 +3224,6 @@
       </c>
       <c r="H5" t="n">
         <v>0.727</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dependency Inversion</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>The domain defines interfaces that are implemented by the infrastructure.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M04_AU20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6701</v>
       </c>
     </row>
   </sheetData>
@@ -3342,7 +3306,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3378,7 +3342,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3414,220 +3378,228 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.8413</v>
+        <v>0.8619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M04_AU18</t>
+          <t>CF_M04_AU19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>backend, authentication service</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Authentication Service</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.7315</v>
+        <v>0.7536</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M04_AU19</t>
+          <t>CF_M04_AU20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>backend, authentication service</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
+          <t>Users: Application customers who use the new features and provide feedback.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>0.7104</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M04_AU20</t>
+          <t>CF_M04_AU21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Users: Application customers who use the new features and provide feedback.</t>
+          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.718</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M04_AU21</t>
+          <t>CF_M04_AU24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>frontend</t>
-        </is>
-      </c>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
+          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Presentation Layer (Frontend)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7078</v>
+        <v>0.9486</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M04_AU24</t>
+          <t>CF_M04_AU26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Google Login</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
+          <t>Authentication services, such as Google login.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Presentation Layer (Frontend)</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9486</v>
+        <v>0.6734</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M04_AU26</t>
+          <t>CF_M04_AU27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Google Login</t>
+          <t>Firebase</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Authentication services, such as Google login.</t>
+          <t>Firebase for complementary functionalities (notifications, services associated).</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6531</v>
+        <v>0.6827</v>
       </c>
     </row>
     <row r="11">
@@ -3654,7 +3626,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3798,16 +3770,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Repository Pattern</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.6841</v>
+        <v>0.7453</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6216</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6897</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7692</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.963</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.375</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8958</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7562</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_02', 'AU_13']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_21</t>
@@ -1233,7 +1245,6 @@
           <t>backend, mysql</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M04_AU04, CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M04_AU25</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Data</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M04_AU23</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1390,13 +1396,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Domain</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M04_AU22</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1472,13 +1474,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Application Layer</t>
@@ -1502,13 +1502,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M04_AU08</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,13 +1552,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Infrastructure Layer</t>
@@ -1584,13 +1580,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1636,13 +1630,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Domain Layer</t>
@@ -1666,13 +1658,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M04_AU07</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1693,7 +1683,6 @@
       <c r="D8" t="n">
         <v>0.9341</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1714,7 +1703,6 @@
           <t>['AU_02', 'AU_09', 'AU_10']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_20</t>
@@ -1725,7 +1713,6 @@
           <t>backend, authentication service, ai service</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1744,7 +1731,6 @@
           <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M04_AU15</t>
@@ -1800,13 +1786,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -1830,13 +1814,11 @@
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M04_AU02</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1857,7 +1839,6 @@
       <c r="D10" t="n">
         <v>0.9972</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1878,7 +1859,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_19</t>
@@ -1889,7 +1869,6 @@
           <t>frontend, backend</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1908,7 +1887,6 @@
           <t>CF_M04_AU01, CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M04_AU29</t>
@@ -1959,14 +1937,11 @@
           <t>71</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Clean Architecture</t>
@@ -1990,13 +1965,11 @@
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2042,13 +2015,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2072,13 +2043,11 @@
           <t>CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M04_AU11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2124,13 +2093,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>REST</t>
@@ -2154,13 +2121,11 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2206,13 +2171,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Authentication Service</t>
@@ -2231,14 +2194,11 @@
       <c r="P14" t="n">
         <v>68</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M04_AU18</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2284,13 +2244,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2314,13 +2272,11 @@
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M04_AU17</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2366,13 +2322,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Factory Pattern</t>
@@ -2396,13 +2350,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M04_P06</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2443,14 +2395,11 @@
           <t>54, 55</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -2469,14 +2418,11 @@
       <c r="P17" t="n">
         <v>55</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2517,14 +2463,11 @@
           <t>54</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -2543,14 +2486,11 @@
       <c r="P18" t="n">
         <v>54</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2596,13 +2536,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Django</t>
@@ -2626,13 +2564,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M04_AU05</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2678,13 +2614,11 @@
           <t>['AU_10']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gemini</t>
@@ -2703,14 +2637,11 @@
       <c r="P20" t="n">
         <v>55</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M04_AU14</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2756,13 +2687,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Repository Pattern</t>
@@ -2786,13 +2715,11 @@
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M04_P05</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2838,13 +2765,11 @@
           <t>['AU_10']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>ChatGPT</t>
@@ -2863,14 +2788,11 @@
       <c r="P22" t="n">
         <v>55</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M04_AU13</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2911,14 +2833,11 @@
           <t>55, 64</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Hexagonal Architecture</t>
@@ -2944,13 +2863,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2996,13 +2913,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Flutter</t>
@@ -3026,13 +2941,11 @@
           <t>CF_M04_AU01, CF_M04_AU03</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M04_AU03</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3106,7 +3019,6 @@
           <t>AI Service</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>External service used for generating intelligent response suggestions for reviews.</t>
@@ -3117,7 +3029,6 @@
           <t>CF_M04_AU15</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.7329</v>
       </c>
@@ -3133,7 +3044,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>frontend, backend</t>
@@ -3174,7 +3084,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>The communication between the front-end and the back-end is carried out through a REST API, using JSON format messages for both requests and responses.</t>
@@ -3185,7 +3094,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7808</v>
       </c>
@@ -3206,7 +3114,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>The system follows a client-server architecture where the mobile application (frontend) makes requests to a server (backend) that processes them.</t>
@@ -3298,7 +3205,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
@@ -3329,7 +3235,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>application layer, domain layer, infrastructure layer</t>
@@ -3365,7 +3270,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>infrastructure layer, gemini</t>
@@ -3381,7 +3285,6 @@
           <t>AU_20</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.8619</v>
       </c>
@@ -3397,7 +3300,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>backend, authentication service</t>
@@ -3438,7 +3340,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Users: Application customers who use the new features and provide feedback.</t>
@@ -3469,7 +3370,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>frontend</t>
@@ -3510,7 +3410,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
@@ -3546,7 +3445,6 @@
           <t>Google Login</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Authentication services, such as Google login.</t>
@@ -3582,7 +3480,6 @@
           <t>Firebase</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Firebase for complementary functionalities (notifications, services associated).</t>
@@ -3613,7 +3510,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>data, backend</t>
@@ -3654,7 +3550,6 @@
           <t>Hierarchical model</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
@@ -3690,7 +3585,6 @@
           <t>Modular architecture</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
@@ -3726,7 +3620,6 @@
           <t>Bloc/Cubit</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>For state and business logic management, the Bloc pattern is used, specificallythrough its Cubit variant, widely used in Flutter applications modern.</t>
@@ -3762,7 +3655,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
@@ -3773,7 +3665,6 @@
           <t>AU_21</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.7453</v>
       </c>
